--- a/clients/encore/testcases/discount-matrix/discount-matrix-location-activation.xlsx
+++ b/clients/encore/testcases/discount-matrix/discount-matrix-location-activation.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="134">
   <si>
     <t>TC ID</t>
   </si>
@@ -334,22 +334,88 @@
     <t>The order is still unchanged</t>
   </si>
   <si>
+    <t>TC-DSM-LOA-012</t>
+  </si>
+  <si>
+    <t>Changing Country swaps the listing to that country's locations</t>
+  </si>
+  <si>
+    <t>The Location Activation tab is open and functionally loaded for office 1604 (rows carry text, not placeholders) with the resting criteria (United States / USD / Standard). No save is involved - a criteria selection is a view switch, never an edit</t>
+  </si>
+  <si>
+    <t>1. With the listing loaded, note the first rows</t>
+  </si>
+  <si>
+    <t>The listing opens on the United States set, `1101 - Corporate Office Encore USA SGA` first</t>
+  </si>
+  <si>
+    <t>2. In the bar above the tabs, change Country to Canada and wait for the rows to reload</t>
+  </si>
+  <si>
+    <t>The page stays on this tab; Currency follows the country on its own, reading `CAD`</t>
+  </si>
+  <si>
+    <t>3. Read the first rows again</t>
+  </si>
+  <si>
+    <t>Canadian locations — the noted United States rows are gone from the top of the listing: the whole listing re-scoped to the new country</t>
+  </si>
+  <si>
+    <t>4. Read the bar's Save</t>
+  </si>
+  <si>
+    <t>Still disabled — choosing a country is navigation, not a pending change</t>
+  </si>
+  <si>
+    <t>5. Change Country back to United States and wait for the rows to reload</t>
+  </si>
+  <si>
+    <t>Currency returns to `USD` and the noted rows are back, `1101 - Corporate Office Encore USA SGA` first</t>
+  </si>
+  <si>
+    <t>TC-DSM-LOA-013</t>
+  </si>
+  <si>
+    <t>The threshold saves from this tab</t>
+  </si>
+  <si>
+    <t>The Location Activation tab is open and functionally loaded for office 1604. Data changes on office 1604 are authorized; the case restores the prior threshold through a verified save before it ends</t>
+  </si>
+  <si>
+    <t>1. With the tab loaded, note the threshold, then type a different in-range value and leave the field</t>
+  </si>
+  <si>
+    <t>The bar's Save enables while this tab is open</t>
+  </si>
+  <si>
+    <t>2. Click the bar's Save, then reload the page</t>
+  </si>
+  <si>
+    <t>The typed value is what the page shows after reload — the save committed from this tab</t>
+  </si>
+  <si>
+    <t>3. Restore the noted threshold with another save and reload</t>
+  </si>
+  <si>
+    <t>The original value is back</t>
+  </si>
+  <si>
     <t>SUMMARY</t>
   </si>
   <si>
     <t>Discount Matrix — Location Activation</t>
   </si>
   <si>
-    <t>Automated: 11 / Pending: 0</t>
-  </si>
-  <si>
-    <t>Pass:11 Fail:0 Skipped:0 Blocked:0</t>
-  </si>
-  <si>
-    <t>Last Updated: 2026-08-27</t>
-  </si>
-  <si>
-    <t>380d8e0d585bd783101a2b952772f0a3767a293b55ceefd229d969fdbd06bb46</t>
+    <t>Automated: 13 / Pending: 0</t>
+  </si>
+  <si>
+    <t>Pass:13 Fail:0 Skipped:0 Blocked:0</t>
+  </si>
+  <si>
+    <t>Last Updated: 2026-08-28</t>
+  </si>
+  <si>
+    <t>cac2701a5bdd1841a1d0e7e6b5d664c8adc61c2fa348a93419b1f3051fe19823</t>
   </si>
 </sst>
 </file>
@@ -738,7 +804,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -2024,45 +2090,373 @@
         <v>25</v>
       </c>
     </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>106</v>
+      </c>
+      <c r="B32" t="s">
+        <v>107</v>
+      </c>
+      <c r="C32" t="s">
+        <v>15</v>
+      </c>
+      <c r="D32" t="s">
+        <v>16</v>
+      </c>
+      <c r="E32" t="s">
+        <v>17</v>
+      </c>
+      <c r="F32" t="s">
+        <v>18</v>
+      </c>
+      <c r="G32" t="s">
+        <v>19</v>
+      </c>
+      <c r="H32" t="s">
+        <v>20</v>
+      </c>
+      <c r="I32" t="s">
+        <v>21</v>
+      </c>
+      <c r="J32" t="s">
+        <v>108</v>
+      </c>
+      <c r="K32" t="s">
+        <v>109</v>
+      </c>
+      <c r="L32" t="s">
+        <v>110</v>
+      </c>
+      <c r="M32" t="s">
+        <v>25</v>
+      </c>
+    </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="I33" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="J33" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K33" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="L33" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M33" s="2" t="s">
-        <v>110</v>
+      <c r="A33" t="s">
+        <v>25</v>
+      </c>
+      <c r="B33" t="s">
+        <v>25</v>
+      </c>
+      <c r="C33" t="s">
+        <v>25</v>
+      </c>
+      <c r="D33" t="s">
+        <v>25</v>
+      </c>
+      <c r="E33" t="s">
+        <v>25</v>
+      </c>
+      <c r="F33" t="s">
+        <v>25</v>
+      </c>
+      <c r="G33" t="s">
+        <v>25</v>
+      </c>
+      <c r="H33" t="s">
+        <v>25</v>
+      </c>
+      <c r="I33" t="s">
+        <v>25</v>
+      </c>
+      <c r="J33" t="s">
+        <v>25</v>
+      </c>
+      <c r="K33" t="s">
+        <v>111</v>
+      </c>
+      <c r="L33" t="s">
+        <v>112</v>
+      </c>
+      <c r="M33" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>25</v>
+      </c>
+      <c r="B34" t="s">
+        <v>25</v>
+      </c>
+      <c r="C34" t="s">
+        <v>25</v>
+      </c>
+      <c r="D34" t="s">
+        <v>25</v>
+      </c>
+      <c r="E34" t="s">
+        <v>25</v>
+      </c>
+      <c r="F34" t="s">
+        <v>25</v>
+      </c>
+      <c r="G34" t="s">
+        <v>25</v>
+      </c>
+      <c r="H34" t="s">
+        <v>25</v>
+      </c>
+      <c r="I34" t="s">
+        <v>25</v>
+      </c>
+      <c r="J34" t="s">
+        <v>25</v>
+      </c>
+      <c r="K34" t="s">
+        <v>113</v>
+      </c>
+      <c r="L34" t="s">
+        <v>114</v>
+      </c>
+      <c r="M34" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>25</v>
+      </c>
+      <c r="B35" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" t="s">
+        <v>25</v>
+      </c>
+      <c r="D35" t="s">
+        <v>25</v>
+      </c>
+      <c r="E35" t="s">
+        <v>25</v>
+      </c>
+      <c r="F35" t="s">
+        <v>25</v>
+      </c>
+      <c r="G35" t="s">
+        <v>25</v>
+      </c>
+      <c r="H35" t="s">
+        <v>25</v>
+      </c>
+      <c r="I35" t="s">
+        <v>25</v>
+      </c>
+      <c r="J35" t="s">
+        <v>25</v>
+      </c>
+      <c r="K35" t="s">
+        <v>115</v>
+      </c>
+      <c r="L35" t="s">
+        <v>116</v>
+      </c>
+      <c r="M35" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>25</v>
+      </c>
+      <c r="B36" t="s">
+        <v>25</v>
+      </c>
+      <c r="C36" t="s">
+        <v>25</v>
+      </c>
+      <c r="D36" t="s">
+        <v>25</v>
+      </c>
+      <c r="E36" t="s">
+        <v>25</v>
+      </c>
+      <c r="F36" t="s">
+        <v>25</v>
+      </c>
+      <c r="G36" t="s">
+        <v>25</v>
+      </c>
+      <c r="H36" t="s">
+        <v>25</v>
+      </c>
+      <c r="I36" t="s">
+        <v>25</v>
+      </c>
+      <c r="J36" t="s">
+        <v>25</v>
+      </c>
+      <c r="K36" t="s">
+        <v>117</v>
+      </c>
+      <c r="L36" t="s">
+        <v>118</v>
+      </c>
+      <c r="M36" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>119</v>
+      </c>
+      <c r="B37" t="s">
+        <v>120</v>
+      </c>
+      <c r="C37" t="s">
+        <v>15</v>
+      </c>
+      <c r="D37" t="s">
+        <v>16</v>
+      </c>
+      <c r="E37" t="s">
+        <v>17</v>
+      </c>
+      <c r="F37" t="s">
+        <v>18</v>
+      </c>
+      <c r="G37" t="s">
+        <v>19</v>
+      </c>
+      <c r="H37" t="s">
+        <v>20</v>
+      </c>
+      <c r="I37" t="s">
+        <v>21</v>
+      </c>
+      <c r="J37" t="s">
+        <v>121</v>
+      </c>
+      <c r="K37" t="s">
+        <v>122</v>
+      </c>
+      <c r="L37" t="s">
+        <v>123</v>
+      </c>
+      <c r="M37" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>25</v>
+      </c>
+      <c r="B38" t="s">
+        <v>25</v>
+      </c>
+      <c r="C38" t="s">
+        <v>25</v>
+      </c>
+      <c r="D38" t="s">
+        <v>25</v>
+      </c>
+      <c r="E38" t="s">
+        <v>25</v>
+      </c>
+      <c r="F38" t="s">
+        <v>25</v>
+      </c>
+      <c r="G38" t="s">
+        <v>25</v>
+      </c>
+      <c r="H38" t="s">
+        <v>25</v>
+      </c>
+      <c r="I38" t="s">
+        <v>25</v>
+      </c>
+      <c r="J38" t="s">
+        <v>25</v>
+      </c>
+      <c r="K38" t="s">
+        <v>124</v>
+      </c>
+      <c r="L38" t="s">
+        <v>125</v>
+      </c>
+      <c r="M38" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>25</v>
+      </c>
+      <c r="B39" t="s">
+        <v>25</v>
+      </c>
+      <c r="C39" t="s">
+        <v>25</v>
+      </c>
+      <c r="D39" t="s">
+        <v>25</v>
+      </c>
+      <c r="E39" t="s">
+        <v>25</v>
+      </c>
+      <c r="F39" t="s">
+        <v>25</v>
+      </c>
+      <c r="G39" t="s">
+        <v>25</v>
+      </c>
+      <c r="H39" t="s">
+        <v>25</v>
+      </c>
+      <c r="I39" t="s">
+        <v>25</v>
+      </c>
+      <c r="J39" t="s">
+        <v>25</v>
+      </c>
+      <c r="K39" t="s">
+        <v>126</v>
+      </c>
+      <c r="L39" t="s">
+        <v>127</v>
+      </c>
+      <c r="M39" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K41" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L41" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M41" s="2" t="s">
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -2078,7 +2472,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>111</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>

--- a/clients/encore/testcases/discount-matrix/discount-matrix-location-activation.xlsx
+++ b/clients/encore/testcases/discount-matrix/discount-matrix-location-activation.xlsx
@@ -415,7 +415,7 @@
     <t>Last Updated: 2026-08-28</t>
   </si>
   <si>
-    <t>cac2701a5bdd1841a1d0e7e6b5d664c8adc61c2fa348a93419b1f3051fe19823</t>
+    <t>f28c807cfb6eeb8b94ac190190f1358c8dc4f8c37d5142ffe46b461a0507db07</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/discount-matrix/discount-matrix-location-activation.xlsx
+++ b/clients/encore/testcases/discount-matrix/discount-matrix-location-activation.xlsx
@@ -415,7 +415,7 @@
     <t>Last Updated: 2026-08-28</t>
   </si>
   <si>
-    <t>f28c807cfb6eeb8b94ac190190f1358c8dc4f8c37d5142ffe46b461a0507db07</t>
+    <t>d96ccb59875274442c18342f06a9aa9c3097f6ed8a4e1cb1fd5e32267acbe42c</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/discount-matrix/discount-matrix-location-activation.xlsx
+++ b/clients/encore/testcases/discount-matrix/discount-matrix-location-activation.xlsx
@@ -415,7 +415,7 @@
     <t>Last Updated: 2026-08-28</t>
   </si>
   <si>
-    <t>d96ccb59875274442c18342f06a9aa9c3097f6ed8a4e1cb1fd5e32267acbe42c</t>
+    <t>49b6bbaa1b0534e99f83598cc30c0c62ecee0b835796d356c2fde35f8e610e29</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/discount-matrix/discount-matrix-location-activation.xlsx
+++ b/clients/encore/testcases/discount-matrix/discount-matrix-location-activation.xlsx
@@ -415,7 +415,7 @@
     <t>Last Updated: 2026-08-28</t>
   </si>
   <si>
-    <t>49b6bbaa1b0534e99f83598cc30c0c62ecee0b835796d356c2fde35f8e610e29</t>
+    <t>a5f7d6500d58722995e66601ec026824ea3e350a07badce9343a7a492d496f36</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/discount-matrix/discount-matrix-location-activation.xlsx
+++ b/clients/encore/testcases/discount-matrix/discount-matrix-location-activation.xlsx
@@ -415,7 +415,7 @@
     <t>Last Updated: 2026-08-28</t>
   </si>
   <si>
-    <t>a5f7d6500d58722995e66601ec026824ea3e350a07badce9343a7a492d496f36</t>
+    <t>636a977849267dc2016113abf29c1c780ee08ec327c6f8ab32a1e036b3a6cf92</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/discount-matrix/discount-matrix-location-activation.xlsx
+++ b/clients/encore/testcases/discount-matrix/discount-matrix-location-activation.xlsx
@@ -415,7 +415,7 @@
     <t>Last Updated: 2026-08-28</t>
   </si>
   <si>
-    <t>636a977849267dc2016113abf29c1c780ee08ec327c6f8ab32a1e036b3a6cf92</t>
+    <t>9b801757218047b86420f352cec3e581306b4bdd9151437dfc89dac28f323abc</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/discount-matrix/discount-matrix-location-activation.xlsx
+++ b/clients/encore/testcases/discount-matrix/discount-matrix-location-activation.xlsx
@@ -5,14 +5,13 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="discount_matrix_loc_activation" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="__fp__" state="hidden" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="133">
   <si>
     <t>TC ID</t>
   </si>
@@ -413,9 +412,6 @@
   </si>
   <si>
     <t>Last Updated: 2026-08-28</t>
-  </si>
-  <si>
-    <t>9b801757218047b86420f352cec3e581306b4bdd9151437dfc89dac28f323abc</t>
   </si>
 </sst>
 </file>
@@ -2463,20 +2459,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
 </file>